--- a/test/excel/xlsx/roundtrip/styles.xlsx
+++ b/test/excel/xlsx/roundtrip/styles.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Library/Containers/com.microsoft.Excel/Data/tmp/fxlsx-71511/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Library/Containers/com.microsoft.Excel/Data/tmp/fxlsx-67743/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{993B3834-1DAD-1943-81C7-95BCB09E85AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6A23490-9F1C-AF4B-B0F1-92137E86310F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -539,7 +539,7 @@
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
     </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:6" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="10" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="2">

--- a/test/excel/xlsx/roundtrip/styles.xlsx
+++ b/test/excel/xlsx/roundtrip/styles.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Library/Containers/com.microsoft.Excel/Data/tmp/fxlsx-67743/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Library/Containers/com.microsoft.Excel/Data/tmp/fxlsx-2614/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6A23490-9F1C-AF4B-B0F1-92137E86310F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF99C0C8-DFEC-9249-A34C-E0B203198A84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -130,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -142,12 +142,17 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" indent="2"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -487,7 +492,7 @@
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="3" width="12.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" style="8"/>
+    <col min="4" max="4" width="8.83203125" style="11"/>
     <col min="6" max="6" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -495,17 +500,17 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="10"/>
+      <c r="C1" s="12"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
     </row>
     <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
@@ -516,10 +521,11 @@
       <c r="A4" s="4">
         <v>1.5</v>
       </c>
+      <c r="D4" s="7"/>
     </row>
     <row r="5" spans="1:6" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
-      <c r="D5" t="s">
+      <c r="D5" s="7" t="s">
         <v>6</v>
       </c>
     </row>
@@ -532,15 +538,19 @@
       <c r="A7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
     </row>
     <row r="9" spans="1:6" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="10"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:C2"/>
